--- a/results/figures_d300.xlsx
+++ b/results/figures_d300.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lsahar/Documents/GitHub_Projects/D300_Coursework/report/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lsahar/Documents/GitHub_Projects/D300_Coursework/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A2AF06-11B2-6B4E-B8A5-CCF221C6774D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACEF8FA-A02A-E84D-A93C-91ABECE76B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="660" windowWidth="27920" windowHeight="17160" activeTab="2" xr2:uid="{BBD4AB09-F6AA-A547-9C0A-EA3A4B093E53}"/>
+    <workbookView xWindow="680" yWindow="660" windowWidth="27920" windowHeight="17160" xr2:uid="{BBD4AB09-F6AA-A547-9C0A-EA3A4B093E53}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -285,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -318,6 +318,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -335,13 +338,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -362,56 +358,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>812800</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>131824</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52DD32A6-71F0-2ED8-7B79-BB70CD9DE8FF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="812800" y="444500"/>
-          <a:ext cx="7772400" cy="5224524"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
@@ -439,7 +385,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -489,7 +435,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -504,6 +450,56 @@
         <a:xfrm>
           <a:off x="21996400" y="444500"/>
           <a:ext cx="9423400" cy="4073198"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>23519</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>34807</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>15173</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{779CB61D-0ADC-5F0E-487C-42401C361983}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="823148" y="435093"/>
+          <a:ext cx="7772400" cy="5224524"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -855,24 +851,24 @@
       </c>
     </row>
     <row r="3" spans="3:21" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="21" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="5"/>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
       <c r="H3" s="5"/>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
     </row>
     <row r="4" spans="3:21" x14ac:dyDescent="0.2">
-      <c r="C4" s="19"/>
+      <c r="C4" s="22"/>
       <c r="D4" s="5"/>
       <c r="E4" s="8" t="s">
         <v>4</v>
@@ -1033,30 +1029,30 @@
       <c r="U8" s="9"/>
     </row>
     <row r="9" spans="3:21" x14ac:dyDescent="0.2">
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="3:21" x14ac:dyDescent="0.2">
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
     </row>
     <row r="20" spans="3:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C20" s="10" t="s">
@@ -1072,24 +1068,24 @@
       <c r="K20" s="7"/>
     </row>
     <row r="21" spans="3:14" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="21" t="s">
         <v>5</v>
       </c>
       <c r="D21" s="5"/>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
       <c r="H21" s="5"/>
-      <c r="I21" s="17" t="s">
+      <c r="I21" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
     </row>
     <row r="22" spans="3:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="19"/>
+      <c r="C22" s="22"/>
       <c r="D22" s="5"/>
       <c r="E22" s="8" t="s">
         <v>4</v>
@@ -1221,28 +1217,28 @@
       <c r="L26" s="1"/>
     </row>
     <row r="27" spans="3:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
     </row>
     <row r="28" spans="3:14" x14ac:dyDescent="0.2">
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
     </row>
     <row r="36" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C36" t="s">
@@ -1399,24 +1395,24 @@
       <c r="J2" s="7"/>
     </row>
     <row r="3" spans="2:14" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="21" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="5"/>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
       <c r="G3" s="5"/>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="19"/>
+      <c r="B4" s="22"/>
       <c r="C4" s="5"/>
       <c r="D4" s="8" t="s">
         <v>4</v>
@@ -1539,28 +1535,28 @@
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.2">
       <c r="N11" t="s">
@@ -1581,24 +1577,24 @@
       <c r="J20" s="7"/>
     </row>
     <row r="21" spans="2:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="21" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="17" t="s">
+      <c r="H21" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B22" s="19"/>
+      <c r="B22" s="22"/>
       <c r="C22" s="5"/>
       <c r="D22" s="8" t="s">
         <v>4</v>
@@ -1721,28 +1717,28 @@
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1761,7 +1757,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1E74D88-CBD3-3644-B42F-DEF0058F92E1}">
-  <dimension ref="B1:AK30"/>
+  <dimension ref="B2:AK30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="15.1640625" customWidth="1"/>
@@ -1769,157 +1765,145 @@
     <col min="37" max="37" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-    </row>
     <row r="2" spans="2:37" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="N2" s="23" t="s">
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="N2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="AA2" s="23" t="s">
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="AA2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="AB2" s="20"/>
-      <c r="AC2" s="20"/>
-      <c r="AD2" s="20"/>
-      <c r="AE2" s="20"/>
-      <c r="AF2" s="20"/>
-      <c r="AG2" s="20"/>
-      <c r="AH2" s="20"/>
-      <c r="AI2" s="20"/>
-      <c r="AJ2" s="20"/>
-      <c r="AK2" s="20"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="14"/>
+      <c r="AJ2" s="14"/>
+      <c r="AK2" s="14"/>
     </row>
     <row r="3" spans="2:37" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="AA3" s="20"/>
-      <c r="AB3" s="20"/>
-      <c r="AC3" s="20"/>
-      <c r="AD3" s="20"/>
-      <c r="AE3" s="20"/>
-      <c r="AF3" s="20"/>
-      <c r="AG3" s="20"/>
-      <c r="AH3" s="20"/>
-      <c r="AI3" s="20"/>
-      <c r="AJ3" s="20"/>
-      <c r="AK3" s="20"/>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="14"/>
+      <c r="AF3" s="14"/>
+      <c r="AG3" s="14"/>
+      <c r="AH3" s="14"/>
+      <c r="AI3" s="14"/>
+      <c r="AJ3" s="14"/>
+      <c r="AK3" s="14"/>
     </row>
     <row r="4" spans="2:37" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="N23" s="14" t="s">
+      <c r="N23" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="14"/>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
-      <c r="U23" s="14"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="14"/>
-      <c r="X23" s="14"/>
-      <c r="AA23" s="14" t="s">
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="17"/>
+      <c r="U23" s="17"/>
+      <c r="V23" s="17"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="17"/>
+      <c r="AA23" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="AB23" s="14"/>
-      <c r="AC23" s="14"/>
-      <c r="AD23" s="14"/>
-      <c r="AE23" s="14"/>
-      <c r="AF23" s="14"/>
-      <c r="AG23" s="14"/>
-      <c r="AH23" s="14"/>
-      <c r="AI23" s="14"/>
-      <c r="AJ23" s="14"/>
-      <c r="AK23" s="14"/>
+      <c r="AB23" s="17"/>
+      <c r="AC23" s="17"/>
+      <c r="AD23" s="17"/>
+      <c r="AE23" s="17"/>
+      <c r="AF23" s="17"/>
+      <c r="AG23" s="17"/>
+      <c r="AH23" s="17"/>
+      <c r="AI23" s="17"/>
+      <c r="AJ23" s="17"/>
+      <c r="AK23" s="17"/>
     </row>
     <row r="24" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="N24" s="24"/>
-      <c r="O24" s="24"/>
-      <c r="P24" s="24"/>
-      <c r="Q24" s="24"/>
-      <c r="R24" s="24"/>
-      <c r="S24" s="24"/>
-      <c r="T24" s="24"/>
-      <c r="U24" s="24"/>
-      <c r="V24" s="24"/>
-      <c r="W24" s="24"/>
-      <c r="X24" s="24"/>
-      <c r="AA24" s="24"/>
-      <c r="AB24" s="24"/>
-      <c r="AC24" s="24"/>
-      <c r="AD24" s="24"/>
-      <c r="AE24" s="24"/>
-      <c r="AF24" s="24"/>
-      <c r="AG24" s="24"/>
-      <c r="AH24" s="24"/>
-      <c r="AI24" s="24"/>
-      <c r="AJ24" s="24"/>
-      <c r="AK24" s="24"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="18"/>
+      <c r="R24" s="18"/>
+      <c r="S24" s="18"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="18"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="18"/>
+      <c r="X24" s="18"/>
+      <c r="AA24" s="18"/>
+      <c r="AB24" s="18"/>
+      <c r="AC24" s="18"/>
+      <c r="AD24" s="18"/>
+      <c r="AE24" s="18"/>
+      <c r="AF24" s="18"/>
+      <c r="AG24" s="18"/>
+      <c r="AH24" s="18"/>
+      <c r="AI24" s="18"/>
+      <c r="AJ24" s="18"/>
+      <c r="AK24" s="18"/>
     </row>
     <row r="28" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
     </row>
     <row r="29" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
     </row>
     <row r="30" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="3">
